--- a/V4_AP1.xlsx
+++ b/V4_AP1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oskar\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197DAE6F-57A2-4347-92E7-5877C19528D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DFA434-68A0-43B8-AF24-3600ACC0D08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="30648" windowHeight="18517" xr2:uid="{C3B10B0A-DC3F-4B20-A1EA-8DCB7EEAD0CB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Messung</t>
   </si>
@@ -47,13 +47,27 @@
   <si>
     <t>AbsoluteAuslenkung</t>
   </si>
+  <si>
+    <t>Gerade</t>
+  </si>
+  <si>
+    <t>Residuum</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -81,8 +95,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -397,10 +412,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E87699-865B-439C-8735-2C5AAA8F6DAA}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -413,12 +428,18 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2">
@@ -428,12 +449,20 @@
         <f>ABS($C$2-C2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f>ROUND(B2*(400/82),3)</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <f>D2-F2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>10</v>
       </c>
       <c r="C3">
@@ -443,12 +472,20 @@
         <f t="shared" ref="D3:D12" si="0">ABS($C$2-C3)</f>
         <v>48.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <f t="shared" ref="F3:F12" si="1">ROUND(B3*(400/82),3)</f>
+        <v>48.78</v>
+      </c>
+      <c r="G3" s="1">
+        <f t="shared" ref="G3:G12" si="2">D3-F3</f>
+        <v>-0.28000000000000114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>20</v>
       </c>
       <c r="C4">
@@ -458,12 +495,20 @@
         <f t="shared" si="0"/>
         <v>97.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>97.561000000000007</v>
+      </c>
+      <c r="G4" s="1">
+        <f t="shared" si="2"/>
+        <v>-6.1000000000007049E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>25</v>
       </c>
       <c r="C5">
@@ -473,12 +518,20 @@
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>121.95099999999999</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0490000000000066</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>30</v>
       </c>
       <c r="C6">
@@ -488,12 +541,20 @@
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>146.34100000000001</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="2"/>
+        <v>0.65899999999999181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>35</v>
       </c>
       <c r="C7">
@@ -503,12 +564,20 @@
         <f t="shared" si="0"/>
         <v>171</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>170.732</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="2"/>
+        <v>0.26800000000000068</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>40</v>
       </c>
       <c r="C8">
@@ -518,12 +587,20 @@
         <f t="shared" si="0"/>
         <v>195.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>195.12200000000001</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="2"/>
+        <v>0.3779999999999859</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>45</v>
       </c>
       <c r="C9">
@@ -533,12 +610,20 @@
         <f t="shared" si="0"/>
         <v>220</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>219.512</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="2"/>
+        <v>0.48799999999999955</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>50</v>
       </c>
       <c r="C10">
@@ -548,12 +633,20 @@
         <f t="shared" si="0"/>
         <v>244</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>243.90199999999999</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="2"/>
+        <v>9.8000000000013188E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>60</v>
       </c>
       <c r="C11">
@@ -563,12 +656,20 @@
         <f t="shared" si="0"/>
         <v>292</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>292.68299999999999</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="2"/>
+        <v>-0.68299999999999272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>70</v>
       </c>
       <c r="C12">
@@ -577,6 +678,14 @@
       <c r="D12">
         <f t="shared" si="0"/>
         <v>341</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>341.46300000000002</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="2"/>
+        <v>-0.46300000000002228</v>
       </c>
     </row>
   </sheetData>
